--- a/SGC-CKN/Excel/6424177f-ec05-4ae9-904e-5b9f80336254_Cọc_khoan_nhồi_-_Trụ_HN_P477_C4_D2000_14-03-2026.xlsx
+++ b/SGC-CKN/Excel/6424177f-ec05-4ae9-904e-5b9f80336254_Cọc_khoan_nhồi_-_Trụ_HN_P477_C4_D2000_14-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="74">
   <si>
     <t>Dự án</t>
   </si>
@@ -98,7 +98,7 @@
     <t>Cát mịn màu xám nâu lẫn bùn sét, kết cấu xốp</t>
   </si>
   <si>
-    <t xml:space="preserve">13:00
+    <t xml:space="preserve">18:00
 13/03/2026</t>
   </si>
   <si>
@@ -162,6 +162,10 @@
   </si>
   <si>
     <t>Cuội, sỏi, sạn cát kết cấu chặt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:30
+14/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">03:30
@@ -263,7 +267,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -290,12 +294,6 @@
     </font>
     <font>
       <color rgb="FF0D3B6E"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -337,7 +335,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -366,7 +364,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -377,11 +375,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDE68A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -492,7 +485,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -518,20 +511,26 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -551,22 +550,13 @@
     <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1158,13 +1148,13 @@
         <v>-8.2</v>
       </c>
       <c r="H11" s="5">
-        <v>5.42</v>
+        <v>0.42</v>
       </c>
       <c r="I11" s="5">
         <v>2.2</v>
       </c>
       <c r="J11" s="8">
-        <v>0.41</v>
+        <v>5.28</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>9</v>
@@ -1233,7 +1223,7 @@
       <c r="I13" s="10">
         <v>2.1</v>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="8">
         <v>5.04</v>
       </c>
       <c r="K13" s="11" t="s">
@@ -1373,7 +1363,7 @@
       <c r="I17" s="10">
         <v>2.1</v>
       </c>
-      <c r="J17" s="13">
+      <c r="J17" s="8">
         <v>5.04</v>
       </c>
       <c r="K17" s="11" t="s">
@@ -1381,614 +1371,614 @@
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="15" t="s">
+      <c r="B18" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="13">
         <v>-18.7</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="13">
         <v>-20.7</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="13">
         <v>0.58</v>
       </c>
-      <c r="I18" s="14">
+      <c r="I18" s="13">
         <v>2</v>
       </c>
       <c r="J18" s="9">
         <v>3.43</v>
       </c>
-      <c r="K18" s="15" t="s">
+      <c r="K18" s="14" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="15" t="s">
+      <c r="B19" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="13">
         <v>-20.7</v>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="13">
         <v>-22.7</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="13">
         <v>1.42</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="13">
         <v>2</v>
       </c>
       <c r="J19" s="9">
         <v>1.41</v>
       </c>
-      <c r="K19" s="15" t="s">
+      <c r="K19" s="14" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="15" t="s">
+      <c r="B20" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="13">
         <v>-22.7</v>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="13">
         <v>-29.7</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="13">
         <v>0.5</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="13">
         <v>7</v>
       </c>
-      <c r="J20" s="13">
+      <c r="J20" s="8">
         <v>14</v>
       </c>
-      <c r="K20" s="15" t="s">
+      <c r="K20" s="14" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="15" t="s">
+      <c r="B21" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="E21" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="13">
         <v>-29.7</v>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="13">
         <v>-31.2</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="13">
         <v>0.58</v>
       </c>
-      <c r="I21" s="14">
+      <c r="I21" s="13">
         <v>1.5</v>
       </c>
       <c r="J21" s="9">
         <v>2.57</v>
       </c>
-      <c r="K21" s="15" t="s">
+      <c r="K21" s="14" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="18" t="s">
+      <c r="B22" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="E22" s="19" t="s">
+      <c r="D22" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="F22" s="17">
+      <c r="E22" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" s="16">
         <v>-31.2</v>
       </c>
-      <c r="G22" s="17">
+      <c r="G22" s="16">
         <v>-33.3</v>
       </c>
-      <c r="H22" s="17">
-        <v>3</v>
-      </c>
-      <c r="I22" s="17">
+      <c r="H22" s="16">
+        <v>2</v>
+      </c>
+      <c r="I22" s="16">
         <v>2.1</v>
       </c>
-      <c r="J22" s="8">
-        <v>0.7</v>
-      </c>
-      <c r="K22" s="18" t="s">
+      <c r="J22" s="9">
+        <v>1.05</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="21" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="23" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B23" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="F23" s="20">
+      <c r="E23" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" s="19">
         <v>-33.3</v>
       </c>
-      <c r="G23" s="20">
+      <c r="G23" s="19">
         <v>-35.3</v>
       </c>
-      <c r="H23" s="20">
+      <c r="H23" s="19">
         <v>0.67</v>
       </c>
-      <c r="I23" s="20">
+      <c r="I23" s="19">
         <v>2</v>
       </c>
       <c r="J23" s="9">
         <v>3</v>
       </c>
-      <c r="K23" s="21" t="s">
+      <c r="K23" s="20" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="21" t="s">
+      <c r="A24" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="B24" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="E24" s="22" t="s">
+      <c r="D24" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="F24" s="20">
+      <c r="E24" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="F24" s="19">
         <v>-35.3</v>
       </c>
-      <c r="G24" s="20">
+      <c r="G24" s="19">
         <v>-37.2</v>
       </c>
-      <c r="H24" s="20">
+      <c r="H24" s="19">
         <v>0.33</v>
       </c>
-      <c r="I24" s="20">
+      <c r="I24" s="19">
         <v>1.9</v>
       </c>
-      <c r="J24" s="13">
+      <c r="J24" s="8">
         <v>5.7</v>
       </c>
-      <c r="K24" s="21" t="s">
+      <c r="K24" s="20" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="21" t="s">
+      <c r="A25" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="D25" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="E25" s="22" t="s">
+      <c r="B25" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="F25" s="20">
+      <c r="E25" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="F25" s="19">
         <v>-37.2</v>
       </c>
-      <c r="G25" s="20">
+      <c r="G25" s="19">
         <v>-39.7</v>
       </c>
-      <c r="H25" s="20">
+      <c r="H25" s="19">
         <v>0.78</v>
       </c>
-      <c r="I25" s="20">
+      <c r="I25" s="19">
         <v>2.5</v>
       </c>
       <c r="J25" s="9">
         <v>3.19</v>
       </c>
-      <c r="K25" s="21" t="s">
+      <c r="K25" s="20" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="21" t="s">
+      <c r="A26" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="D26" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="E26" s="22" t="s">
+      <c r="B26" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="F26" s="20">
+      <c r="E26" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26" s="19">
         <v>-39.7</v>
       </c>
-      <c r="G26" s="20">
+      <c r="G26" s="19">
         <v>-41.4</v>
       </c>
-      <c r="H26" s="20">
+      <c r="H26" s="19">
         <v>0.47</v>
       </c>
-      <c r="I26" s="20">
+      <c r="I26" s="19">
         <v>1.7</v>
       </c>
       <c r="J26" s="9">
         <v>3.64</v>
       </c>
-      <c r="K26" s="21" t="s">
+      <c r="K26" s="20" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="21" t="s">
+      <c r="A27" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="D27" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="E27" s="22" t="s">
+      <c r="B27" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="F27" s="20">
+      <c r="E27" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="F27" s="19">
         <v>-41.4</v>
       </c>
-      <c r="G27" s="20">
+      <c r="G27" s="19">
         <v>-43.5</v>
       </c>
-      <c r="H27" s="20">
+      <c r="H27" s="19">
         <v>0.5</v>
       </c>
-      <c r="I27" s="20">
+      <c r="I27" s="19">
         <v>2.1</v>
       </c>
       <c r="J27" s="9">
         <v>4.2</v>
       </c>
-      <c r="K27" s="21" t="s">
+      <c r="K27" s="20" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="21" t="s">
+      <c r="A28" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="D28" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="E28" s="22" t="s">
+      <c r="B28" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="F28" s="20">
+      <c r="E28" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28" s="19">
         <v>-43.5</v>
       </c>
-      <c r="G28" s="20">
+      <c r="G28" s="19">
         <v>-45.7</v>
       </c>
-      <c r="H28" s="20">
+      <c r="H28" s="19">
         <v>0.33</v>
       </c>
-      <c r="I28" s="20">
+      <c r="I28" s="19">
         <v>2.2</v>
       </c>
-      <c r="J28" s="13">
+      <c r="J28" s="8">
         <v>6.6</v>
       </c>
-      <c r="K28" s="21" t="s">
+      <c r="K28" s="20" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="21" t="s">
+      <c r="A29" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="D29" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="E29" s="22" t="s">
+      <c r="B29" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="F29" s="20">
+      <c r="E29" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="F29" s="19">
         <v>-45.7</v>
       </c>
-      <c r="G29" s="20">
+      <c r="G29" s="19">
         <v>-47.1</v>
       </c>
-      <c r="H29" s="20">
+      <c r="H29" s="19">
         <v>0.5</v>
       </c>
-      <c r="I29" s="20">
+      <c r="I29" s="19">
         <v>1.4</v>
       </c>
       <c r="J29" s="9">
         <v>2.8</v>
       </c>
-      <c r="K29" s="21" t="s">
+      <c r="K29" s="20" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="21" t="s">
+      <c r="A30" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="D30" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="E30" s="22" t="s">
+      <c r="B30" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="F30" s="20">
+      <c r="E30" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="F30" s="19">
         <v>-47.1</v>
       </c>
-      <c r="G30" s="20">
+      <c r="G30" s="19">
         <v>-49.3</v>
       </c>
-      <c r="H30" s="20">
+      <c r="H30" s="19">
         <v>0.42</v>
       </c>
-      <c r="I30" s="20">
+      <c r="I30" s="19">
         <v>2.2</v>
       </c>
-      <c r="J30" s="13">
+      <c r="J30" s="8">
         <v>5.28</v>
       </c>
-      <c r="K30" s="21" t="s">
+      <c r="K30" s="20" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="21" t="s">
+      <c r="A31" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="D31" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="E31" s="22" t="s">
+      <c r="B31" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D31" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="F31" s="20">
+      <c r="E31" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="F31" s="19">
         <v>-49.3</v>
       </c>
-      <c r="G31" s="20">
+      <c r="G31" s="19">
         <v>-51.6</v>
       </c>
-      <c r="H31" s="20">
+      <c r="H31" s="19">
         <v>0.5</v>
       </c>
-      <c r="I31" s="20">
+      <c r="I31" s="19">
         <v>2.3</v>
       </c>
       <c r="J31" s="9">
         <v>4.6</v>
       </c>
-      <c r="K31" s="21" t="s">
+      <c r="K31" s="20" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B32" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="21" t="s">
+      <c r="A32" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="D32" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="E32" s="22" t="s">
+      <c r="B32" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="20">
+      <c r="E32" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="F32" s="19">
         <v>-51.6</v>
       </c>
-      <c r="G32" s="20">
+      <c r="G32" s="19">
         <v>-53.4</v>
       </c>
-      <c r="H32" s="20">
+      <c r="H32" s="19">
         <v>0.75</v>
       </c>
-      <c r="I32" s="20">
+      <c r="I32" s="19">
         <v>1.8</v>
       </c>
       <c r="J32" s="9">
         <v>2.4</v>
       </c>
-      <c r="K32" s="21" t="s">
+      <c r="K32" s="20" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="21" t="s">
+      <c r="A33" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E33" s="22" t="s">
+      <c r="B33" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D33" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="F33" s="20">
+      <c r="E33" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="F33" s="19">
         <v>-53.4</v>
       </c>
-      <c r="G33" s="20">
+      <c r="G33" s="19">
         <v>-55.2</v>
       </c>
-      <c r="H33" s="20">
+      <c r="H33" s="19">
         <v>0.58</v>
       </c>
-      <c r="I33" s="20">
+      <c r="I33" s="19">
         <v>1.8</v>
       </c>
       <c r="J33" s="9">
         <v>3.09</v>
       </c>
-      <c r="K33" s="21" t="s">
+      <c r="K33" s="20" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B34" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="21" t="s">
+      <c r="A34" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="D34" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="E34" s="22" t="s">
+      <c r="B34" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="F34" s="20">
+      <c r="E34" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="F34" s="19">
         <v>-55.2</v>
       </c>
-      <c r="G34" s="20">
+      <c r="G34" s="19">
         <v>-57</v>
       </c>
-      <c r="H34" s="20">
+      <c r="H34" s="19">
         <v>0.92</v>
       </c>
-      <c r="I34" s="20">
+      <c r="I34" s="19">
         <v>1.8</v>
       </c>
       <c r="J34" s="9">
         <v>1.96</v>
       </c>
-      <c r="K34" s="21" t="s">
+      <c r="K34" s="20" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="B37" s="23"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
-      <c r="H37" s="23"/>
-      <c r="I37" s="23"/>
-      <c r="J37" s="23"/>
-      <c r="K37" s="23"/>
+      <c r="A37" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="22"/>
     </row>
     <row r="38" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="39" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2083,31 +2073,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2130,13 +2120,13 @@
         <v>-9.2</v>
       </c>
       <c r="G2" s="5">
-        <v>5.83</v>
+        <v>0.83</v>
       </c>
       <c r="H2" s="5">
         <v>3.2</v>
       </c>
-      <c r="I2" s="8">
-        <v>0.55</v>
+      <c r="I2" s="9">
+        <v>3.84</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2169,28 +2159,28 @@
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="14">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="15" t="s">
+      <c r="B4" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="13">
         <v>4</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="13">
         <v>-18.7</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="13">
         <v>-31.2</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="13">
         <v>3.08</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="13">
         <v>12.5</v>
       </c>
       <c r="I4" s="9">
@@ -2198,57 +2188,57 @@
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="17">
+      <c r="A5" s="16">
         <v>4</v>
       </c>
-      <c r="B5" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="18" t="s">
+      <c r="B5" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="16">
         <v>1</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="16">
         <v>-31.2</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="16">
         <v>-33.3</v>
       </c>
-      <c r="G5" s="17">
-        <v>3</v>
-      </c>
-      <c r="H5" s="17">
+      <c r="G5" s="16">
+        <v>2</v>
+      </c>
+      <c r="H5" s="16">
         <v>2.1</v>
       </c>
-      <c r="I5" s="8">
-        <v>0.7</v>
+      <c r="I5" s="9">
+        <v>1.05</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="20">
+      <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="20">
+      <c r="B6" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="19">
         <v>12</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="19">
         <v>-33.3</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="19">
         <v>-57</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="19">
         <v>6.75</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="19">
         <v>23.7</v>
       </c>
       <c r="I6" s="9">
@@ -2256,32 +2246,32 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="25">
+      <c r="A7" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="24">
         <v>24</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="24">
         <v>-6</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="24">
         <v>-57</v>
       </c>
-      <c r="G7" s="25">
-        <v>21.25</v>
-      </c>
-      <c r="H7" s="25">
+      <c r="G7" s="24">
+        <v>15.25</v>
+      </c>
+      <c r="H7" s="24">
         <v>51</v>
       </c>
-      <c r="I7" s="25">
-        <v>2.4</v>
+      <c r="I7" s="24">
+        <v>3.34</v>
       </c>
     </row>
   </sheetData>
